--- a/Tabela1_clusters.xlsx
+++ b/Tabela1_clusters.xlsx
@@ -504,7 +504,7 @@
         <v>0.612117</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.029806</v>
+        <v>0.059611</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>6</v>
@@ -521,7 +521,7 @@
         <v>0.157131</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.03846</v>
+        <v>0.07692</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>13</v>
